--- a/output/Data and Chart Outputs/south_america_gas_balance.xlsx
+++ b/output/Data and Chart Outputs/south_america_gas_balance.xlsx
@@ -1374,7 +1374,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Latest month per sheet: {'Production': 'Aug-26', 'Imports': 'Aug-26', 'Exports': 'Sep-26', 'Apparent supply': 'Aug-26'}</t>
+          <t>Latest month per sheet: {'Production': 'Aug-26', 'Imports': 'Sep-26', 'Exports': 'Sep-26', 'Apparent supply': 'Aug-26'}</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9049,6 +9049,14 @@
       </c>
       <c r="E69" t="n">
         <v>10.17</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1.748</v>
       </c>
     </row>
   </sheetData>
@@ -10243,6 +10251,9 @@
       <c r="A70" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="B70" t="n">
+        <v>3.934</v>
+      </c>
       <c r="D70" t="n">
         <v>13.691</v>
       </c>
@@ -12305,7 +12316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K608"/>
+  <dimension ref="A1:K609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25916,13 +25927,38 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="E608" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="G608" t="n">
+        <v>3.934</v>
+      </c>
+      <c r="I608" t="n">
+        <v>1.748</v>
+      </c>
+      <c r="J608" t="n">
+        <v>3.934</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
           <t>Peru</t>
         </is>
       </c>
-      <c r="H608" t="n">
+      <c r="H609" t="n">
         <v>13.691</v>
       </c>
-      <c r="J608" t="n">
+      <c r="J609" t="n">
         <v>13.691</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/south_america_gas_balance.xlsx
+++ b/output/Data and Chart Outputs/south_america_gas_balance.xlsx
@@ -161,6 +161,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>South America gas production by country (to Dec/25)</a:t>
             </a:r>
           </a:p>
@@ -492,6 +493,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>South America gas imports by country (pipeline + LNG) (to Mar/26)</a:t>
             </a:r>
           </a:p>
@@ -767,7 +769,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>South America gas exports by country (pipeline + LNG) (to May/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>South America gas exports by country (pipeline + LNG) (to Jun/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -797,12 +800,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Exports'!$A$2:$A$66</f>
+              <f>'Chart - Exports'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Exports'!$B$2:$B$66</f>
+              <f>'Chart - Exports'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -825,12 +828,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Exports'!$A$2:$A$66</f>
+              <f>'Chart - Exports'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Exports'!$C$2:$C$66</f>
+              <f>'Chart - Exports'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -853,12 +856,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Exports'!$A$2:$A$66</f>
+              <f>'Chart - Exports'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Exports'!$D$2:$D$66</f>
+              <f>'Chart - Exports'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -881,12 +884,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Exports'!$A$2:$A$66</f>
+              <f>'Chart - Exports'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Exports'!$E$2:$E$66</f>
+              <f>'Chart - Exports'!$E$2:$E$67</f>
             </numRef>
           </val>
         </ser>
@@ -1374,7 +1377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Latest month per sheet: {'Production': 'Aug-26', 'Imports': 'Sep-26', 'Exports': 'Sep-26', 'Apparent supply': 'Aug-26'}</t>
+          <t>Latest month per sheet: {'Production': 'Sep-26', 'Imports': 'Sep-26', 'Exports': 'Sep-26', 'Apparent supply': 'Sep-26'}</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5718,6 +5721,23 @@
       </c>
       <c r="E66" t="n">
         <v>33.146</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8.757999999999999</v>
+      </c>
+      <c r="C67" t="n">
+        <v>12.922</v>
+      </c>
+      <c r="D67" t="n">
+        <v>16.146</v>
+      </c>
+      <c r="E67" t="n">
+        <v>26.109</v>
       </c>
     </row>
   </sheetData>
@@ -5732,7 +5752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7530,6 +7550,9 @@
       <c r="H67" t="n">
         <v>43.94</v>
       </c>
+      <c r="I67" t="n">
+        <v>62.044</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -7563,6 +7586,14 @@
       </c>
       <c r="H69" t="n">
         <v>46.413</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F70" t="n">
+        <v>19.37</v>
       </c>
     </row>
   </sheetData>
@@ -8991,7 +9022,7 @@
         <v>14.981</v>
       </c>
       <c r="D66" t="n">
-        <v>20.22</v>
+        <v>19.892</v>
       </c>
       <c r="E66" t="n">
         <v>8.01</v>
@@ -9011,7 +9042,7 @@
         <v>13.042</v>
       </c>
       <c r="D67" t="n">
-        <v>20.17</v>
+        <v>19.792</v>
       </c>
       <c r="E67" t="n">
         <v>8.5</v>
@@ -9031,10 +9062,13 @@
         <v>18.809</v>
       </c>
       <c r="D68" t="n">
-        <v>22.55</v>
+        <v>22.232</v>
       </c>
       <c r="E68" t="n">
         <v>8.98</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.411</v>
       </c>
     </row>
     <row r="69">
@@ -9047,6 +9081,9 @@
       <c r="C69" t="n">
         <v>14.822</v>
       </c>
+      <c r="D69" t="n">
+        <v>13.737</v>
+      </c>
       <c r="E69" t="n">
         <v>10.17</v>
       </c>
@@ -9056,7 +9093,13 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>1.748</v>
+        <v>1.929</v>
+      </c>
+      <c r="C70" t="n">
+        <v>9.446999999999999</v>
+      </c>
+      <c r="E70" t="n">
+        <v>12.37</v>
       </c>
     </row>
   </sheetData>
@@ -10218,6 +10261,9 @@
       <c r="D67" t="n">
         <v>16.146</v>
       </c>
+      <c r="E67" t="n">
+        <v>26.109</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -10252,7 +10298,7 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>3.934</v>
+        <v>4.545</v>
       </c>
       <c r="D70" t="n">
         <v>13.691</v>
@@ -10269,7 +10315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12267,6 +12313,9 @@
       <c r="H67" t="n">
         <v>27.794</v>
       </c>
+      <c r="I67" t="n">
+        <v>35.934</v>
+      </c>
       <c r="J67" t="n">
         <v>0.441</v>
       </c>
@@ -12287,6 +12336,9 @@
       <c r="H68" t="n">
         <v>28.485</v>
       </c>
+      <c r="J68" t="n">
+        <v>0.411</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -12303,6 +12355,14 @@
       </c>
       <c r="H69" t="n">
         <v>30.652</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="F70" t="n">
+        <v>31.74</v>
       </c>
     </row>
   </sheetData>
@@ -12316,7 +12376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K609"/>
+  <dimension ref="A1:K614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25378,11 +25438,14 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="F581" t="n">
-        <v>20.22</v>
+      <c r="D581" t="n">
+        <v>11.476</v>
+      </c>
+      <c r="E581" t="n">
+        <v>8.416</v>
       </c>
       <c r="I581" t="n">
-        <v>20.22</v>
+        <v>19.892</v>
       </c>
     </row>
     <row r="582">
@@ -25567,11 +25630,14 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="F590" t="n">
-        <v>20.17</v>
+      <c r="D590" t="n">
+        <v>13.494</v>
+      </c>
+      <c r="E590" t="n">
+        <v>6.298</v>
       </c>
       <c r="I590" t="n">
-        <v>20.17</v>
+        <v>19.792</v>
       </c>
     </row>
     <row r="591">
@@ -25640,42 +25706,39 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="D594" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="I594" t="n">
-        <v>0.441</v>
+          <t>Trinidad &amp; Tobago</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>62.044</v>
+      </c>
+      <c r="H594" t="n">
+        <v>26.109</v>
+      </c>
+      <c r="J594" t="n">
+        <v>26.109</v>
       </c>
       <c r="K594" t="n">
-        <v>0.441</v>
+        <v>35.934</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="4" t="n">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D595" t="n">
-        <v>1.152</v>
-      </c>
-      <c r="E595" t="n">
-        <v>14.426</v>
-      </c>
-      <c r="G595" t="n">
-        <v>8.550000000000001</v>
+        <v>0.441</v>
       </c>
       <c r="I595" t="n">
-        <v>15.577</v>
-      </c>
-      <c r="J595" t="n">
-        <v>8.550000000000001</v>
+        <v>0.441</v>
+      </c>
+      <c r="K595" t="n">
+        <v>0.441</v>
       </c>
     </row>
     <row r="596">
@@ -25684,14 +25747,23 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Bolivia</t>
-        </is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="E596" t="n">
+        <v>14.426</v>
       </c>
       <c r="G596" t="n">
-        <v>10.8</v>
+        <v>8.550000000000001</v>
+      </c>
+      <c r="I596" t="n">
+        <v>15.577</v>
       </c>
       <c r="J596" t="n">
-        <v>10.8</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="597">
@@ -25700,23 +25772,14 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="C597" t="n">
-        <v>66.96299999999999</v>
-      </c>
-      <c r="D597" t="n">
-        <v>8.885</v>
-      </c>
-      <c r="E597" t="n">
-        <v>9.923999999999999</v>
-      </c>
-      <c r="I597" t="n">
-        <v>18.809</v>
-      </c>
-      <c r="K597" t="n">
-        <v>85.77200000000001</v>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="G597" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J597" t="n">
+        <v>10.8</v>
       </c>
     </row>
     <row r="598">
@@ -25725,14 +25788,23 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Chile</t>
-        </is>
-      </c>
-      <c r="F598" t="n">
-        <v>22.55</v>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>66.96299999999999</v>
+      </c>
+      <c r="D598" t="n">
+        <v>8.885</v>
+      </c>
+      <c r="E598" t="n">
+        <v>9.923999999999999</v>
       </c>
       <c r="I598" t="n">
-        <v>22.55</v>
+        <v>18.809</v>
+      </c>
+      <c r="K598" t="n">
+        <v>85.77200000000001</v>
       </c>
     </row>
     <row r="599">
@@ -25741,20 +25813,17 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="C599" t="n">
-        <v>20.16</v>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>11.541</v>
       </c>
       <c r="E599" t="n">
-        <v>8.98</v>
+        <v>10.691</v>
       </c>
       <c r="I599" t="n">
-        <v>8.98</v>
-      </c>
-      <c r="K599" t="n">
-        <v>29.14</v>
+        <v>22.232</v>
       </c>
     </row>
     <row r="600">
@@ -25763,14 +25832,20 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C600" t="n">
-        <v>0.6889999999999999</v>
+        <v>20.16</v>
+      </c>
+      <c r="E600" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="I600" t="n">
+        <v>8.98</v>
       </c>
       <c r="K600" t="n">
-        <v>0.6889999999999999</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="601">
@@ -25779,61 +25854,55 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C601" t="n">
-        <v>44.028</v>
-      </c>
-      <c r="H601" t="n">
-        <v>15.544</v>
-      </c>
-      <c r="J601" t="n">
-        <v>15.544</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K601" t="n">
-        <v>28.485</v>
+        <v>0.6889999999999999</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="4" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="D602" t="n">
-        <v>2.888</v>
-      </c>
-      <c r="E602" t="n">
-        <v>6.661</v>
-      </c>
-      <c r="G602" t="n">
-        <v>6.282</v>
-      </c>
-      <c r="I602" t="n">
-        <v>9.548999999999999</v>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>44.028</v>
+      </c>
+      <c r="H602" t="n">
+        <v>15.544</v>
       </c>
       <c r="J602" t="n">
-        <v>6.282</v>
+        <v>15.544</v>
+      </c>
+      <c r="K602" t="n">
+        <v>28.485</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="4" t="n">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="G603" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="J603" t="n">
-        <v>11.48</v>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="I603" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="K603" t="n">
+        <v>0.411</v>
       </c>
     </row>
     <row r="604">
@@ -25842,23 +25911,23 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="C604" t="n">
-        <v>70.29000000000001</v>
+          <t>Argentina</t>
+        </is>
       </c>
       <c r="D604" t="n">
-        <v>7.61</v>
+        <v>2.888</v>
       </c>
       <c r="E604" t="n">
-        <v>7.212</v>
+        <v>6.661</v>
+      </c>
+      <c r="G604" t="n">
+        <v>6.282</v>
       </c>
       <c r="I604" t="n">
-        <v>14.822</v>
-      </c>
-      <c r="K604" t="n">
-        <v>85.11199999999999</v>
+        <v>9.548999999999999</v>
+      </c>
+      <c r="J604" t="n">
+        <v>6.282</v>
       </c>
     </row>
     <row r="605">
@@ -25867,20 +25936,14 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="C605" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="E605" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="I605" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="K605" t="n">
-        <v>30.08</v>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="G605" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="J605" t="n">
+        <v>11.48</v>
       </c>
     </row>
     <row r="606">
@@ -25889,14 +25952,23 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C606" t="n">
-        <v>0.666</v>
+        <v>70.29000000000001</v>
+      </c>
+      <c r="D606" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="E606" t="n">
+        <v>7.212</v>
+      </c>
+      <c r="I606" t="n">
+        <v>14.822</v>
       </c>
       <c r="K606" t="n">
-        <v>0.666</v>
+        <v>85.11199999999999</v>
       </c>
     </row>
     <row r="607">
@@ -25905,60 +25977,155 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="C607" t="n">
-        <v>46.413</v>
-      </c>
-      <c r="H607" t="n">
-        <v>15.761</v>
-      </c>
-      <c r="J607" t="n">
-        <v>15.761</v>
-      </c>
-      <c r="K607" t="n">
-        <v>30.652</v>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>8.923999999999999</v>
+      </c>
+      <c r="E607" t="n">
+        <v>4.813</v>
+      </c>
+      <c r="I607" t="n">
+        <v>13.737</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="4" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="D608" t="n">
-        <v>1.464</v>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>19.91</v>
       </c>
       <c r="E608" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="G608" t="n">
-        <v>3.934</v>
+        <v>10.17</v>
       </c>
       <c r="I608" t="n">
-        <v>1.748</v>
-      </c>
-      <c r="J608" t="n">
-        <v>3.934</v>
+        <v>10.17</v>
+      </c>
+      <c r="K608" t="n">
+        <v>30.08</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="K609" t="n">
+        <v>0.666</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>46.413</v>
+      </c>
+      <c r="H610" t="n">
+        <v>15.761</v>
+      </c>
+      <c r="J610" t="n">
+        <v>15.761</v>
+      </c>
+      <c r="K610" t="n">
+        <v>30.652</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="4" t="n">
         <v>46266</v>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>1.645</v>
+      </c>
+      <c r="E611" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="G611" t="n">
+        <v>4.545</v>
+      </c>
+      <c r="I611" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="J611" t="n">
+        <v>4.545</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>9.446999999999999</v>
+      </c>
+      <c r="I612" t="n">
+        <v>9.446999999999999</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="E613" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="I613" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="K613" t="n">
+        <v>31.74</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B614" t="inlineStr">
         <is>
           <t>Peru</t>
         </is>
       </c>
-      <c r="H609" t="n">
+      <c r="H614" t="n">
         <v>13.691</v>
       </c>
-      <c r="J609" t="n">
+      <c r="J614" t="n">
         <v>13.691</v>
       </c>
     </row>
